--- a/Adressliste_Event_EcoFlow.xlsx
+++ b/Adressliste_Event_EcoFlow.xlsx
@@ -143,8 +143,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Adressen" displayName="Adressen" ref="A1:K92" headerRowCount="1">
-  <autoFilter ref="A1:K92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Adressen" displayName="Adressen" ref="A1:K156" headerRowCount="1">
+  <autoFilter ref="A1:K156"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Nr."/>
     <tableColumn id="2" name="Firma"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -1927,50 +1927,54 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VOK DAMS Events GmbH</t>
+          <t>DS-Veranstaltungstechnik GmbH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Katernberger Straße 54</t>
+          <t>Mercedesstraße 2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>42115</t>
+          <t>74366</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wuppertal</t>
+          <t>Kirchheim am Neckar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Eventagentur</t>
+          <t>Licht-/Ton-/Bühnentechnik Verleih &amp; Full-Service</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://www.vokdams.de</t>
+          <t>https://www.ds-veranstaltungstechnik.de</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Live-Marketing-Events weltweit, oft Outdoor-Locations ohne Netzanschluss</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>Referenzfirma, seit 1994, ca. 20 MA, mobile Bühnen, Planungsbüro Heilbronn</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>E-Mail-Domain ds-veranstaltung.de</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1978,47 +1982,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Uniplan GmbH &amp; Co. KG</t>
+          <t>LMB-Showtechnik</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Schanzenstraße 39 a/b</t>
+          <t>Kreuzäckerstraße 35</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>51063</t>
+          <t>74081</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Heilbronn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Eventagentur / Messebau</t>
+          <t>Licht-/Tontechnik Verleih &amp; Verkauf</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://www.uniplan.com</t>
+          <t>https://lmb-showtechnik.de</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Markenerlebnisse und Messestände, temporäre Installationen brauchen Strom</t>
+          <t>Inhabergeführt (M. Borgmann), seit 1995, Partys bis Bühnen im Landkreis</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2029,52 +2033,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LIGHTEQUIP GmbH &amp; Co. KG</t>
+          <t>PA-Technik-Team Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wilhelm-Mauser-Straße 41-43</t>
+          <t>Postfach 241</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>74206</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Bad Wimpfen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik (Verleih/Handel Film und Event)</t>
+          <t>PA-/Lichtverleih &amp; DJ-Service</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://www.lightequip.de</t>
+          <t>https://www.pa-technik-team.de</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Führt bereits mobile Energiespeicher im Sortiment, Händler- oder Vermietpotenzial</t>
+          <t>Kleiner PA-Verleih mit DJ-Service, Raum Bad Rappenau/Neckarsulm</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Führt bereits Energiespeicher – evtl. Wettbewerber/Händlerpartner</t>
+          <t>Nur Postfach bekannt – Adresse telefonisch klären (07063 2679658)</t>
         </is>
       </c>
     </row>
@@ -2084,47 +2088,47 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SOUND BROS. GmbH</t>
+          <t>media:system</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ettore-Bugatti-Str. 43</t>
+          <t>Röntgenstraße 21</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>74613</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Öhringen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik (Ton/Licht-Verleih)</t>
+          <t>Licht-/Ton-/Lasertechnik Verleih, Dry Hire &amp; Full-Service</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://www.soundbros.de</t>
+          <t>https://mediasystem.de</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Ton- und Lichtverleih, leiser Strom für Open-Air-Einsätze</t>
+          <t>Inhabergeführt (M. Hammel), auch Privat-/DJ-Kunden, Hohenlohe</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2135,54 +2139,50 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Procon Event GmbH (Procon Veranstaltungstechnik)</t>
+          <t>Music-Light Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eygelshovener Straße 10</t>
+          <t>Frankenstraße 10</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>74549</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Wolpertshausen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Ton-/Licht-/Bühnentechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://procon-veranstaltungstechnik.de</t>
+          <t>https://music-light.de</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Licht-Ton-Bühnentechnik für Events, Ersatz für laute Generatoren</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Verzeichnisse nennen noch Frangenheimstraße</t>
-        </is>
-      </c>
+          <t>Hohenlohe/Schwäbisch Hall, Ton, Licht, Bühne aus einer Hand</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2190,47 +2190,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Parookaville GmbH</t>
+          <t>JF Eventtechnik</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Katharinenquartier 4-6</t>
+          <t>Jägerstraße 16</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>47652</t>
+          <t>74369</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Weeze</t>
+          <t>Löchgau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Licht-/Ton-/Bühnentechnik Verleih &amp; Full-Service</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://www.parookaville.com</t>
+          <t>https://www.jf-eventtechnik.com</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Großfestival mit Camping, Bühnen, Food-Ständen, hoher mobiler Strombedarf</t>
+          <t>Inhaber Jochen Friedrich, Hochzeiten und Komplettpakete, nahe Besigheim</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2241,47 +2241,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Raum3 Konzertveranstaltungs GmbH (Haldern Pop)</t>
+          <t>NE Eventtechnik</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lindenstraße 1b</t>
+          <t>Hirtenwiesen 94</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>46459</t>
+          <t>74343</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rees-Haldern</t>
+          <t>Sachsenheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Ton-/Licht-/Bühnentechnik Verleih, Komplettpakete</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://haldernpop.com</t>
+          <t>https://ne-eventtechnik.de</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Ländliches Open-Air-Festival, emissionsfreie Stromversorgung für Nebenbühnen</t>
+          <t>Kleiner Verleih für Hochzeiten/Geburtstage, Einzugsgebiet bis Brackenheim</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2292,50 +2292,54 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Contour Festival Organisations GmbH (Summerjam)</t>
+          <t>Soundlight Company GmbH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hemmelrather Weg 241</t>
+          <t>Planckstraße 17</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>51377</t>
+          <t>71665</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Vaihingen an der Enz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Audio-/Licht-/Medien-/Bühnentechnik Full-Service</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://summerjam.de</t>
+          <t>https://www.soundlight.tv</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Open-Air am Fühlinger See, Stromversorgung für Bühnen und Stände</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Mittelständischer Eventtechnik-Dienstleister, Kreis Ludwigsburg</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Büro Planckstr. 21</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2343,52 +2347,52 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>satis&amp;fy AG</t>
+          <t>Meier Eventservice</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Industriegebiet Dögelmühle</t>
+          <t>Im Mohn 10</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>61184</t>
+          <t>70806</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karben</t>
+          <t>Kornwestheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hessen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik / Bühnenbau / Eventproduktion</t>
+          <t>Ton-/Licht-/Medientechnik, Bühne &amp; DJ-Service</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://satis-fy.com</t>
+          <t>https://www.meier-eventservice.de</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Großer Eventdienstleister mit Nachhaltigkeitsfokus, Dieselersatz für Produktionen</t>
+          <t>Inhaber Daniel Meier, Bürgerfeste, Public Viewing, Open Airs</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Keine Hausnummer im Impressum</t>
+          <t>Impressum-Stand ca. 4,5 Jahre alt – vor Versand prüfen</t>
         </is>
       </c>
     </row>
@@ -2398,47 +2402,47 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Röder Zelt- und Veranstaltungsservice GmbH</t>
+          <t>FE-Events</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Am Lautenstein 5</t>
+          <t>Bussardstraße 27</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>63654</t>
+          <t>74889</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Büdingen</t>
+          <t>Sinsheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hessen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Zeltverleih / Mobile Raumlösungen</t>
+          <t>PA-/Licht-/Bühnenverleih, LED-Wand, Eventzubehör</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://roder.com</t>
+          <t>https://www.feevents.de</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Temporäre Hallen und VIP-Zelte benötigen netzunabhängige Stromversorgung</t>
+          <t>Inhaber Falk Engelhardt, Gartenparty bis Firmenevent, liefert nach Heilbronn</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2449,50 +2453,54 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FKP Zelt-Event GmbH</t>
+          <t>EuroTronic Veranstaltungstechnik UG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Im Steinböhl 9</t>
+          <t>Hauptstraße 2</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>69518</t>
+          <t>74889</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Abtsteinach</t>
+          <t>Sinsheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hessen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Zeltverleih</t>
+          <t>Licht-/Ton-/Bühnentechnik, Zeltbau, Festinstallation</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://fkp-zelte.de</t>
+          <t>https://www.eurotronic-veranstaltungstechnik.de</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Fest- und Eventzelte, leiser Strom für Beleuchtung und Catering</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Kleiner Full-Service-Betrieb, Bühnen- und Zeltbau, Kraichgau</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Verzeichnisse nennen Schwimmbadweg 46 – vor Versand prüfen</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2500,50 +2508,54 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WORLD CLUB DOME GmbH</t>
+          <t>Maximilian Egner Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Schwedlerstraße 1-5</t>
+          <t>Üttingshöfer Steige 5</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>97980</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Bad Mergentheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hessen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Veranstaltungstechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://www.worldclubdome.com</t>
+          <t>https://egner-veranstaltungstechnik.de</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Großevents mit vielen Bühnen und Backstage-Strombedarf</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>Inhabergeführter Kleinbetrieb, Main-Tauber-Kreis</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Website im Umbau</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2551,50 +2563,54 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I-Motion GmbH Events &amp; Communication (Nature One)</t>
+          <t>Chris Only Entertainment / TONLYGHTS Event Technik</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Am Hohen Stein 8</t>
+          <t>Roggenbergstraße 3</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>56218</t>
+          <t>97980</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mülheim-Kärlich</t>
+          <t>Bad Mergentheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>DJ- &amp; Eventtechnik, PA, Licht, Bühnenpodeste</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>https://www.nature-one.de</t>
+          <t>https://chris-only.de</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Festival auf ehemaligem Raketengelände, große Camping- und Floorflächen</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>DJ plus Technikverleih, Festivals und Hochzeiten, Main-Tauber</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Website nennt auch Giebelstadt und Wittighausen</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2602,47 +2618,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MBE Licht- und Tontechnik (Marcus Bochert)</t>
+          <t>Tonartist-Event Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hauptstraße 12</t>
+          <t>Brunnenstraße 1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>56598</t>
+          <t>69242</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rheinbrohl</t>
+          <t>Mühlhausen (OT Rettigheim)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Licht-/Ton-Pakete inkl. Aufbau</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://www.mbe-licht-ton.de</t>
+          <t>https://www.tonartist-event.de</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Licht- und Tontechnik für Vereins- und Stadtfeste ohne Stromanschluss</t>
+          <t>Inhabergeführt, Pakete 50–1000 Personen, Rhein-Neckar/Kraichgau</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -2653,47 +2669,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>M. Franzreb &amp; Söhne GmbH &amp; Co. KG</t>
+          <t>Mediapool Stuttgart GmbH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sachsenhütter Straße 8</t>
+          <t>Im Langen Feld 22</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bad Dürkheim</t>
+          <t>Althütte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Zeltverleih / Zeltbau</t>
+          <t>Ton-/Licht-/Videotechnik Verleih &amp; Installation</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://franzreb-zelte.de</t>
+          <t>https://www.mediapool-stuttgart.de</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Festzeltbetrieb für Weinfeste, Strom für Licht und Ausschank</t>
+          <t>Kleiner Dienstleister, Rems-Murr, Backnang bis Stuttgart</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -2704,47 +2720,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zeltverleih Ernst GmbH</t>
+          <t>Gierss. Veranstaltungstechnik GmbH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rat-Tressel-Straße 29b</t>
+          <t>Karolingerstraße 23</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>66636</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tholey</t>
+          <t>Waiblingen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Zeltverleih</t>
+          <t>Ton-/Licht-/Video-/Bühnentechnik Full-Service &amp; Verleih</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://www.zeltverleih-ernst.de</t>
+          <t>https://gierss.de</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Party- und Festzelte, Strom für private und gewerbliche Feiern</t>
+          <t>Etablierter Mittelständler Rems-Murr, Open Airs und Firmenevents</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2755,50 +2771,54 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Saar-Lor-Lux-Zelte GmbH &amp; Co. KG</t>
+          <t>Kuehner Events GbR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Konrad-Zuse-Straße 8</t>
+          <t>Brühlstraße 19</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>66459</t>
+          <t>73271</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kirkel</t>
+          <t>Holzmaden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Zeltverleih / Eventlogistik / Catering</t>
+          <t>Licht-/Ton-/Medientechnik, Dekoverleih, Mietpark</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://saar-lor-lux-zelte.eu</t>
+          <t>https://www.kuehner-events.de</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Zelte, Zeltheizungen und Catering-Verbund, hoher mobiler Strombedarf</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Familienbetrieb Kühner, viele Hochzeiten, Raum Kirchheim/Teck</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Tritt als Betrieb aus Kirchheim/Teck auf</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2806,47 +2826,47 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Laut &amp; Leise Veranstaltungstechnik (Dirk Langer)</t>
+          <t>Tecksound Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hochwaldstraße 34</t>
+          <t>Alte Kirchheimer Straße 36</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>73230</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Losheim am See</t>
+          <t>Kirchheim unter Teck (Nabern)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik (PA/Licht/Bühne-Verleih)</t>
+          <t>Ton-/Lichttechnik Verleih, Traversenbau</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://www.llv-langer.de</t>
+          <t>https://www.tecksound.de</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Vermietung PA, Licht und Bühnen, mobile Stromlösung als Zusatzangebot</t>
+          <t>Zwei Inhaber, kleiner Verleih mit Beratung vor Ort</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -2857,52 +2877,52 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Presented for People GmbH &amp; Co. KG (Rocco del Schlacko)</t>
+          <t>AG Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europaallee 6</t>
+          <t>In den Kreuzäckern 11</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>66113</t>
+          <t>73101</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saarbrücken</t>
+          <t>Aichelberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Festival- und Konzertveranstalter</t>
+          <t>Licht/Ton/Medien/Rigging/Bühnenbau Full-Service</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://www.rocco-del-schlacko.de</t>
+          <t>https://www.ag-vt.com</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Open-Air-Veranstalter, Strombedarf für Bühnen und Gelände</t>
+          <t>Stadtfeste, Konzerte bis 10.000 Personen, inhabergeführt</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Festival laut Website beendet – schwacher Lead</t>
+          <t>Andere Seiten nennen Albstraße 1, 73274 Notzingen; evtl. selber Inhaber wie UBS Quality Sound</t>
         </is>
       </c>
     </row>
@@ -2912,47 +2932,47 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WOA Festival GmbH (Wacken Open Air)</t>
+          <t>ATLANTIS Ton- und Lichtsysteme e.K.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Schenefelder Str. 17</t>
+          <t>Vordere Mühlstraße 28</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>25596</t>
+          <t>73035</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wacken</t>
+          <t>Göppingen-Faurndau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Verleih, Verkauf &amp; Full-Service Showtechnik</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://www.wacken.com</t>
+          <t>https://atlantis-technik.de</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Riesiges Festivalgelände mit vielen Bühnen und Camping, hoher Bedarf an Dieselersatz</t>
+          <t>Abhol- oder Fullservice, Firmenfeiern und Jubiläen, Göppingen</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -2963,47 +2983,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FKP Scorpio Konzertproduktionen GmbH</t>
+          <t>TUSMON Eventmanagement GbR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Große Elbstraße 277a</t>
+          <t>Hausgärtenweg 3</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>73054</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Eislingen/Fils</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Licht-/Ton-Mietshop, DJ, Events</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://fkpscorpio.com</t>
+          <t>https://www.tusmon.de</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Veranstaltet Hurricane und weitere Open-Airs, hat eine Nachhaltigkeitsstrategie</t>
+          <t>Junger Betrieb seit 2019, günstige Mietpakete, Hochzeiten/Partys</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3014,47 +3034,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LCe Event &amp; Technik GmbH</t>
+          <t>music &amp; light design GmbH (mld)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ottensener Straße 8</t>
+          <t>Bruckenbachstraße 34</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>71229</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Leonberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Veranstaltungstechnik Verleih, Dry Hire &amp; Full-Service</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://lce-hamburg.de</t>
+          <t>https://www.mld.de</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ton-, Licht- und Messetechnik, mobiler Strom für Außeneinsätze</t>
+          <t>Mittelständischer Verleiher Kreis Böblingen, Ton, Licht, Medien</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3065,47 +3085,47 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Karsten Jahnke Konzertdirektion GmbH</t>
+          <t>EventPARK Schlegel Veranstaltungstechnik GbR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lerchenstraße 12</t>
+          <t>Im Letten 28/1</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>71139</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Ehningen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Konzert- und Festivalveranstalter</t>
+          <t>Ton/Licht/Bühne/Medien Mietpark &amp; Service</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://kj.de</t>
+          <t>https://www.eventpark-schlegel.de</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Open-Air-Konzerte brauchen leise Stromversorgung für Bühne und Backstage</t>
+          <t>Brüder Schlegel, seit 2000, eigener Mietpark inkl. Bühnen</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3116,54 +3136,50 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kopf &amp; Steine GmbH (MS Dockville)</t>
+          <t>SPLISS Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eduardstraße 46</t>
+          <t>Laußnitzer Weg 12</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>71134</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Aidlingen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Licht-/Ton-/Videotechnik Verleih &amp; Full-Service</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://msdockville.de</t>
+          <t>https://spliss-online.de</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Festival auf Industriebrache, Nachbarn verlangen leise und emissionsfreie Stromquellen</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Impressum evtl. älter</t>
-        </is>
-      </c>
+          <t>Meisterbetrieb seit 1995, Raum Böblingen/Sindelfingen/Herrenberg</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3171,47 +3187,47 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ESK Events &amp; Promotion GmbH (Deichbrand)</t>
+          <t>Light&amp;Audio-Service Schlotter-Seibold GbR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Otto-Lilienthal-Straße 1</t>
+          <t>Grünewaldstraße 11</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>71083</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wurster Nordseeküste</t>
+          <t>Herrenberg-Gültstein</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Niedersachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Ton-/Lichttechnik Verleih &amp; DJ-Service</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://deichbrand.de</t>
+          <t>https://www.lightaudio-service.de</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Großes Festival auf einem Flugplatz ohne festes Stromnetz</t>
+          <t>Zwei Inhaber, Hochzeiten, Firmenfeiern, Open-Air-Bühnen</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3222,47 +3238,47 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kulturkosmos Müritz e.V. (Fusion Festival)</t>
+          <t>Stefan Turata TTS GmbH (TTS event)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Am Flugplatz 1</t>
+          <t>Max-Eyth-Straße 6</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>71144</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lärz</t>
+          <t>Steinenbronn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mecklenburg-Vorpommern</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Mobile Bühnen, Licht, Ton, Medien, DJ</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>https://fusion-festival.de</t>
+          <t>https://www.tts-event.de</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Festival mit Öko-Anspruch und vielen dezentralen Bühnen ohne Netzanschluss</t>
+          <t>Inhabergeführt, mobile Bühnen und DJ, Großraum Stuttgart</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3273,47 +3289,47 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Airbeat One GmbH Zweigniederlassung</t>
+          <t>LTM Licht Ton Medientechnik GmbH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paulstraße 2a</t>
+          <t>Siedlung 11-13</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>75196</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lübtheen</t>
+          <t>Remchingen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mecklenburg-Vorpommern</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Event-/Konferenz-/Kongresstechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>https://airbeat-one.de</t>
+          <t>https://online-ltm.de</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Großes Elektrofestival mit Campingflächen, Strom für Infrastruktur nötig</t>
+          <t>Regionaler Dienstleister Enzkreis/Karlsruhe, bewirbt auch Raum Heilbronn</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3324,47 +3340,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hannover Concerts GmbH &amp; Co. KG Betriebsgesellschaft</t>
+          <t>SOUNDWAVE Veranstaltungstechnik (Max Atzig)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ferdinand-Wilhelm-Fricke-Weg 8</t>
+          <t>Eichenweg 30</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>75228</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hannover</t>
+          <t>Ispringen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Niedersachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Konzertveranstalter</t>
+          <t>PA-, Licht- &amp; DJ-Equipment Verleih</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>https://www.hannover-concerts.de</t>
+          <t>https://soundwave-pa.de</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Betreibt Open-Air-Bühnen und -Konzerte, Strom für Nebenflächen</t>
+          <t>Junger Inhaberbetrieb, Hochzeitstechnik, Pforzheim/Enzkreis/Karlsruhe</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3375,50 +3391,54 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rent.Group Hamburg/Bremen GmbH (Party.Rent Hamburg)</t>
+          <t>HZ Eventtechnik</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Senefelder-Ring 80</t>
+          <t>Haydnstraße 23</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>75181</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Reinbek</t>
+          <t>Pforzheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Eventmobiliar-Verleih</t>
+          <t>Licht-/Tontechnik für Konzerte &amp; Events</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>https://www.partyrent.com/de/eventverleih-hamburg</t>
+          <t>https://www.hz-eventtechnik.de</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Verleiht Eventausstattung, Powerstations wären eine sinnvolle Ergänzung im Mietsortiment</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>Kleiner Eventtechnik-Dienstleister Pforzheim</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Adresse von Startseite, Impressum nicht gelesen</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3426,50 +3446,54 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Störtebeker Festspiele GmbH &amp; Co. KG</t>
+          <t>BW Sound &amp; Light (Benjamin Weschenfelder)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Am Bodden 100</t>
+          <t>Heiliggutweg 3</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>76689</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ralswiek</t>
+          <t>Karlsdorf-Neuthard</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mecklenburg-Vorpommern</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Open-Air-Veranstalter</t>
+          <t>Ton-/Licht-/Effekttechnik Verleih</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>https://www.stoertebeker.de</t>
+          <t>https://www.bw-sound.de</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Naturbühne im Landschaftsschutzgebiet, dort zählen leise und emissionsfreie Stromquellen</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>Ein-Mann-Verleih, Hochzeiten/Firmenfeiern, Raum Bruchsal</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Ältere Seite nennt Schumannstraße 30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3477,54 +3501,50 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Reload Event GmbH</t>
+          <t>Rent a PA (Benjamin Merk)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rudolf-Diesel-Straße 5</t>
+          <t>Westring 25</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>76698</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sulingen</t>
+          <t>Ubstadt-Weiher</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Niedersachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>PA-/Lichtverleih, Partysets &amp; Komplettservice</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>https://reload-festival.de</t>
+          <t>https://www.rentapa.de</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Metal-Festival auf freiem Gelände, braucht Strom für Camping und Stände</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Adresse aus Shop-AGB/Datenschutz</t>
-        </is>
-      </c>
+          <t>Kleiner Verleih mit Hochzeitssets, Bruchsal/Karlsruhe</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3532,47 +3552,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Baltic Eventmanagement GmbH (Baltic Open Air)</t>
+          <t>Symetry Veranstaltungstechnik e.K.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Schmiederedder 8</t>
+          <t>Dischingerstraße 2a</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>69123</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fleckeby</t>
+          <t>Heidelberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Ton-/Licht-/Bühnen-/Medientechnik</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>https://www.baltic-open-air.de</t>
+          <t>https://symetry.de</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Open-Air auf freier Fläche, braucht mobile Stromversorgung</t>
+          <t>Einzelunternehmen (S. Ihle), Full-Service Heidelberg</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3583,47 +3603,47 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HAMKE Event &amp; Messe (Jan-Mirko Hamke)</t>
+          <t>AC-Eventtechnik Horsch-Stuntz GbR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dorfstraße 150</t>
+          <t>Albert-Lortzing-Straße 7</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>69214</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Klein Nordende</t>
+          <t>Eppelheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Veranstaltungs- und Messetechnik</t>
+          <t>Licht-/Tontechnik, Dry Hire &amp; Service</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>https://hamke.biz</t>
+          <t>https://ac-eventtechnik.de</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Event- und Messetechnik, mobile Akkus für Außeneinsätze</t>
+          <t>Zwei Inhaber, private Feiern bis Live-Band-Events</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -3634,52 +3654,52 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Otter Veranstaltungstechnik GbR</t>
+          <t>wivent (Andrea Wilhelm)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Haart 224</t>
+          <t>Breslauer Straße 10</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>24539</t>
+          <t>68723</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neumünster</t>
+          <t>Schwetzingen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik und Bühnenbau</t>
+          <t>Verleih Veranstaltungstechnik, Sound &amp; Eventorganisation</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>https://www.otter-veranstaltungstechnik.de</t>
+          <t>https://wivent.de</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Vermietet Licht, Ton und Bühnen, Strom als Zusatzmietartikel</t>
+          <t>Inhabergeführt, Verleih seit 2010, Events bis 4.000 Personen</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Laut Website keine Abholadresse</t>
+          <t>Adresse von Startseite, Impressum nicht gelesen</t>
         </is>
       </c>
     </row>
@@ -3689,50 +3709,54 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Großmarkt Rostock GmbH</t>
+          <t>Lite-Tech Veranstaltungstechnik GmbH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hanseatenstraße 5</t>
+          <t>Reichenbachstraße 17-19</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>68309</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rostock</t>
+          <t>Mannheim</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mecklenburg-Vorpommern</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Markt- und Großveranstalter</t>
+          <t>Licht/Ton/Video/Rigging/Bühne Full-Service &amp; Verleih</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>https://www.grossmarkt-rostock.de</t>
+          <t>https://lite-tech.de</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Veranstaltet Weihnachts- und Spezialmärkte, Marktstände brauchen mobilen Strom</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>Über 25 Jahre, Full-Service und Rental, Rhein-Neckar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Adresse aus Mietkatalog 2023</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3740,50 +3764,54 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MEISSNER EXPO GmbH</t>
+          <t>UBS Quality Sound (Alexander Fischer)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Industriestraße 11</t>
+          <t>Im Loh 39</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>73434</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Halstenbek</t>
+          <t>Aalen-Fachsenfeld</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Messebau</t>
+          <t>Sound/Light/Stage/Effekte Verleih, Verkauf, Betreuung</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>https://meissner-expo.de</t>
+          <t>https://www.ubs-quality-sound.de</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Nachhaltiger Messebauer, Strom für Outdoor-Stände und Aufbauphasen</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>Inhabergeführt, Stadtfeste Aalen, Ostalbkreis</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Evtl. selber Inhaber wie AG Veranstaltungstechnik</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3791,54 +3819,50 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZELTCITY GmbH &amp; Co. KG</t>
+          <t>DSR Veranstaltungstechnik GmbH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jägerstieg 5</t>
+          <t>Ferdinand-Lassalle-Straße 41</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>72770</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wentorf bei Hamburg</t>
+          <t>Reutlingen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Zeltverleih</t>
+          <t>Licht-/Ton-/Bühnentechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>https://www.zeltcity.de</t>
+          <t>https://dsr-net.de</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Zeltveranstaltungen auf Freiflächen brauchen Strom für Licht und Catering</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>PLZ nicht direkt im Impressum bestätigt</t>
-        </is>
-      </c>
+          <t>Inhabergeführter Full-Service-Betrieb, regionale Events, Verleihlager Reutlingen</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3846,47 +3870,47 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bührmann Gruppe GmbH</t>
+          <t>Tecstage GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hamfhofsweg 133</t>
+          <t>Stübeweg 53a</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>28357</t>
+          <t>79108</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Freiburg im Breisgau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Event und Gastronomie</t>
+          <t>Veranstaltungstechnik Verleih &amp; Service (Mietshop)</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>https://buehrmann-gruppe.de</t>
+          <t>https://www.tecstage.de</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Eventlocation Lankenauer Höft und Catering, Strom für Außen- und Strandevents</t>
+          <t>Ton/Licht/Bühne-Verleih mit Mietshop, Stadt- und Kulturevents Freiburg</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -3897,50 +3921,54 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CK Catering Kontor Hamburg GmbH</t>
+          <t>da-sound PA-Verleih &amp; Eventservice</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ausschläger Weg 36-38</t>
+          <t>Wormser Str. 23</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>20537</t>
+          <t>64319</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Pfungstadt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Hessen</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Event-Catering</t>
+          <t>PA-Verleih / DJ- &amp; Eventservice</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>https://cateringkontor.de</t>
+          <t>https://www.da-sound.de</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Catering bis 4000 Gäste, mobiler Strom für Außenküchen</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>Vermietet bereits Benzin-Stromaggregate: direkter Ersatz durch Akkuspeicher</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Vermietet Benzin-Aggregate (Top-Lead); Lager Werner-von-Siemens-Str. 2, Pfungstadt</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3948,50 +3976,54 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Frontsound Veranstaltungstechnik GmbH</t>
+          <t>Huss Licht &amp; Ton GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Stöhrerstraße 3e</t>
+          <t>Carl-Zeiss-Straße 6</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>04347</t>
+          <t>89129</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Langenau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Veranstaltungstechnik Handel &amp; Verleih</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>https://www.frontsound.de</t>
+          <t>https://www.huss-licht-ton.de</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ton-, Licht- und Videotechnik bei Events braucht leisen mobilen Strom</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>Großer Regionalanbieter bei Ulm, Verleih und Shop für Eventtechnik</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Großer Händler (nur Kleinakkus, keine Großspeicher) – auch als Vertriebspartner denkbar</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3999,47 +4031,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Messeprojekt GmbH</t>
+          <t>Max Eventtechnik</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bergweg 7</t>
+          <t>Zergleweg 4</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>04356</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Konstanz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Messebau</t>
+          <t>Licht-/LED-/Rigging-Verleih</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>https://messeprojekt.de</t>
+          <t>https://max-eventtechnik.de</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Messestände und Events brauchen emissionsfreien Strom in Hallen</t>
+          <t>Inhabergeführt (Fachkraft VT), Licht/LED, Events am Bodensee</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4050,47 +4082,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>dd show &amp; eventgroup</t>
+          <t>smidtaudio Veranstaltungstechnik e.K.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wirtschaftsweg 2a</t>
+          <t>Philipp-Reis-Straße 18</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>04420</t>
+          <t>78052</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Markranstädt</t>
+          <t>Villingen-Schwenningen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bühnenbau/Eventvermietung</t>
+          <t>Tontechnik / Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>https://www.eventmodul-vermietung.de</t>
+          <t>https://smidtaudio.de</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Mobile Bühnen und Showküchen im Freien brauchen netzunabhängigen Strom</t>
+          <t>Kleiner inhabergeführter Ton-/Eventtechnikbetrieb Schwarzwald-Baar</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4101,50 +4133,54 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nachtdigital GmbH</t>
+          <t>AE Audio-Express Veranstaltungstechnik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Friedensstr. 20</t>
+          <t>Lampengasse 4/1</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>04774</t>
+          <t>89610</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dahlen</t>
+          <t>Oberdischingen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Licht-/Ton-/Bühnentechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>https://nachtdigital.de</t>
+          <t>https://www.audio-express.de</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Open-Air-Festival im Grünen mit Bedarf an leisen Stromquellen</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>Seit über 35 Jahren in Region Ulm, Lager Einsingen/Ulm</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Impressum-Stand 1-4 Jahre alt – vor Versand prüfen</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4152,50 +4188,54 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HMG Events GmbH &amp; Co. KG</t>
+          <t>LSD Ton- &amp; Lichtverleih</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>An der Prießnitzaue 32</t>
+          <t>Kolpingstr. 37</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>01328</t>
+          <t>64653</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dresden</t>
+          <t>Lorsch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Hessen</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bühnenbau/Eventausstattung</t>
+          <t>PA-/Licht-Verleih</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>https://www.hmg-rentals.de</t>
+          <t>https://www.lsd-verleih.de</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Bühnen- und Infrastrukturverleih für Open Airs ohne Netzanschluss</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>Verleih an Private/Vereine, bietet Akku-Lautsprecher: Outdoor-Strombedarf vorhanden</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Impressum nennt auch Kirchstr. 29, 68623 Lampertheim</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4203,50 +4243,54 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PAW pa-world GmbH (Turbo Events)</t>
+          <t>Soundstation Freiburg</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Behringstr. 34</t>
+          <t>Mittlere Straße 12</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>01159</t>
+          <t>79292</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dresden</t>
+          <t>Pfaffenweiler</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Licht-/Ton-Verleih, Firmenfeiern</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>https://turbo-events.de</t>
+          <t>https://www.soundstation-freiburg.de</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fullservice-Eventtechnik braucht Strom an Orten ohne Netzanschluss</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>Verleih für Firmenfeiern/Partys, Abhollager Freiburg Wiesentalstraße</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Büro; Lager/Abholung Wiesentalstr. 29, 79115 Freiburg</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4254,47 +4298,47 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nuck GmbH</t>
+          <t>inventhaus Veranstaltungstechnik (Michael Fäth)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nikolaus-Otto-Str. 11</t>
+          <t>Bollenwaldstraße 113</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02625</t>
+          <t>63743</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bautzen</t>
+          <t>Aschaffenburg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Zeltverleih</t>
+          <t>Veranstaltungstechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>https://www.nuck.de</t>
+          <t>http://www.inventhaus.de</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Festzelte und Bühnen brauchen Beleuchtungs- und Cateringstrom</t>
+          <t>Inhabergeführter Verleih- und Servicebetrieb Unterfranken</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4305,50 +4349,54 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Der Event Service</t>
+          <t>Event-Xpress.com GmbH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bahnhofstraße 4</t>
+          <t>Markgraf-Wilhelm-Str. 44</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>09228</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chemnitz</t>
+          <t>Gaggenau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>DJ- &amp; Eventtechnik</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>https://www.der-event-service.de</t>
+          <t>https://www.event-xpress.com</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Ton, Licht und Bühne mit Mietpark für Außenveranstaltungen</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>DJ-Service mit Technikverleih, Hochzeiten und Firmenfeiern Raum Rastatt</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Büro; Sitz laut Impressum Hindenburgstr. 6a</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4356,47 +4404,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>tec4you GbR</t>
+          <t>CRS-Lightning Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Schönherrstraße 8</t>
+          <t>Borsigstraße 32</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>09113</t>
+          <t>91058</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chemnitz</t>
+          <t>Erlangen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sachsen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik/Mobilbühnen</t>
+          <t>Licht-/Ton-/Medientechnik Verleih</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>https://tec4you.eu</t>
+          <t>https://www.crs-lightning.de</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Mobilbühnen bundesweit im Einsatz brauchen leise Stromversorgung</t>
+          <t>Kleinbetrieb mit Mietkatalog und Komplettpaketen, Mittelfranken</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -4407,47 +4455,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>blue media event GmbH</t>
+          <t>AudioLights Veranstaltungstechnik (Oliver Buck)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wichertstraße 47</t>
+          <t>Eschweg 9</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Ravensburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Licht-/Ton-/DJ-Technik</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>https://blue-media.de</t>
+          <t>https://www.audiolights.de</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Berliner Eventtechnikverleih – Innenstadtevents ohne Dieselgenerator</t>
+          <t>Inhabergeführt, Licht/Ton/DJ für Feste in Oberschwaben</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -4458,47 +4506,47 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VEITLIGHT Martin Veit</t>
+          <t>Viewpoint Event &amp; Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Möllendorffstr. 52</t>
+          <t>Karlstraße 7</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>76437</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Rastatt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Licht- und Tontechnikverleih</t>
+          <t>Licht-/Tonanlagen-Verleih</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>https://licht-und-tontechnikverleih.de</t>
+          <t>https://www.viewpoint-technik.de</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Licht und Ton für Partys im Freien in Berlin-Brandenburg</t>
+          <t>Licht- und Beschallungsverleih mit Mietpool, Raum Rastatt/Baden-Baden</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4509,47 +4557,47 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rorbach Event + Sound</t>
+          <t>Tischler Veranstaltungstechnik (Achim Tischler)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Havelländer Ring 38</t>
+          <t>Unterer Hammer 3</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>64720</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Michelstadt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Hessen</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Licht-/Ton-/Bühnentechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>https://rorbach-events.com</t>
+          <t>http://www.tischler-veranstaltungstechnik.de</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Konferenz- und Eventtechnik braucht leise Pufferstromlösung</t>
+          <t>Inhabergeführter Odenwald-Betrieb, ländliche Feste ohne Stromanschluss</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -4560,54 +4608,50 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GATE Eventmanagement &amp; Veranstaltungstechnik GmbH</t>
+          <t>Meyer Eventtechnik (Sebastian Meyer)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salzufer 13-14a</t>
+          <t>Heid 18</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>77855</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Achern</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Eventagentur/Veranstaltungstechnik</t>
+          <t>Ton-/Licht-/Bühnentechnik</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>https://gate-av.de</t>
+          <t>https://meyer-eventtechnik.de</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Eventmanagement mit Technik für Locations mit schwachem Netzanschluss</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Kontaktseite nennt auch Reuchlinstr. 10-11, 10553 Berlin</t>
-        </is>
-      </c>
+          <t>Inhabergeführt, Licht/Ton/Bühne für Events in Ortenau</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4615,52 +4659,52 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rentboks</t>
+          <t>H-Light Veranstaltungstechnik (Oliver Hub)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lise-Meitner-Straße 39a</t>
+          <t>Dachsgrube 15A</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>97526</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Sennfeld</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Mobiler Strom-/Soundverleih</t>
+          <t>Licht-/Ton-Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>https://www.rentboks.de</t>
+          <t>https://www.h-light.de</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Verleiht bereits Powerstations und könnte Großspeicher ins Mietangebot aufnehmen</t>
+          <t>Inhabergeführter Licht-/Tonbetrieb Raum Schweinfurt</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Andere Seiten nennen Nr. 41; verleiht bereits Powerstations</t>
+          <t>Adresse von Kontaktseite (Lager); Büro Am Wall 36, 97525 Schwebheim</t>
         </is>
       </c>
     </row>
@@ -4670,47 +4714,47 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zeltverleih Heinz Pautz</t>
+          <t>EMSL Eberhardt Media Sound &amp; Light</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Alt-Lübars 38a</t>
+          <t>Kapuzinergarten 1</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>72108</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Rottenburg am Neckar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Zeltverleih</t>
+          <t>Ton-/Licht-Verleih</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>https://www.zeltverleih-pautz.de</t>
+          <t>https://www.emsl.de</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Fest- und Partyzelte brauchen Strom für Licht und Catering</t>
+          <t>Inhabergeführt, Veranstaltungstechnik-Verleih Raum Tübingen</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -4721,50 +4765,54 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Berliner Partyservice Grunke</t>
+          <t>ICEVT Event &amp; Veranstaltungstechnik</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Müllerstr. 185</t>
+          <t>Burgstraße 12</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>91781</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Weißenburg in Bayern</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Catering/Imbisswagenverleih</t>
+          <t>Veranstaltungstechnik Verleih</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>https://eventcatering-grunke.de</t>
+          <t>https://www.icevt.de</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Verleiht Imbiss- und Kühlwagen, die netzunabhängigen Strom brauchen</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>Kleiner Eventtechnik-Verleih Altmühlfranken, Volks- und Vereinsfeste</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Kein Impressum gefunden – Adresse aus Websitedaten</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4772,54 +4820,50 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DTB Veranstaltungstechnik GmbH</t>
+          <t>I/O Event GbR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ricarda-Huch-Straße 2</t>
+          <t>Baumackerweg 14</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>79541</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Potsdam</t>
+          <t>Lörrach</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Licht-/Veranstaltungstechnik Verleih</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>https://www.dtb.berlin</t>
+          <t>https://www.io-event.com</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Fullservice inklusive Stromversorgung für Events in Brandenburg</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Lager: Am Buchhorst 33, 14478 Potsdam</t>
-        </is>
-      </c>
+          <t>Inhabergeführt, Verleih im 75-km-Umkreis Lörrach</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4827,47 +4871,47 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ferropolis Stiftung Industriekultur gGmbH</t>
+          <t>HVT Hochrhein Veranstaltungstechnik (Jörg Winkler)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ferropolisstrasse 1</t>
+          <t>Kupferschmidstraße 76</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>06773</t>
+          <t>79761</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Gräfenhainichen</t>
+          <t>Waldshut-Tiengen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Festivalgelände/Veranstalter</t>
+          <t>Licht-/Ton-Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>https://www.ferropolis.de</t>
+          <t>https://www.h-v-t.de</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Großes Festivalgelände mit hohem temporärem Strombedarf</t>
+          <t>Inhabergeführter Licht-/Tonbetrieb Hochrhein</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -4878,52 +4922,52 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Expovent</t>
+          <t>BMS Veranstaltungstechnik GmbH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Leipziger Chaussee 193</t>
+          <t>Fritz-Schieler-Str. 8</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>06112</t>
+          <t>79331</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Halle (Saale)</t>
+          <t>Teningen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Eventausstattung/Veranstaltungstechnik</t>
+          <t>Sound &amp; Light, Zeltverleih</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>https://expovent.de</t>
+          <t>https://www.bms-sound.de</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Verleiht Bühnen, Zelte und Technik, die Strom brauchen</t>
+          <t>Ton/Licht plus Zeltverleih: typische Outdoor-Feste mit Strombedarf</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Impressum ca. 6 Jahre alt – vor Versand prüfen</t>
+          <t>Impressum-Stand 1-4 Jahre alt – vor Versand prüfen</t>
         </is>
       </c>
     </row>
@@ -4933,54 +4977,50 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ESS Emmes Sound Service</t>
+          <t>JSE Show- und Eventtechnik GmbH</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Holleber Weg 14</t>
+          <t>Karbacherstr. 16</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>06128</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Halle (Saale)</t>
+          <t>Marktheidenfeld</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Licht-/Ton-/Medientechnik Verleih, Vertrieb</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>https://www.ess-veranstaltungstechnik.de</t>
+          <t>https://jse-eventtechnik.de</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Bühnen-, Licht- und Tontechnik für Events in Halle</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Adresse am schwächsten belegt – vor Versand prüfen</t>
-        </is>
-      </c>
+          <t>Kleiner Verleih-/Installationsbetrieb Main-Spessart</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4988,47 +5028,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Showsystem Fabian Stankewitz</t>
+          <t>ZEPRA Event GmbH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Satteldorfer Straße 13</t>
+          <t>Simon-Breu-Straße 44</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>97074</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gröningen</t>
+          <t>Würzburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik/Zeltverleih</t>
+          <t>Eventagentur mit Licht/Ton- und Zeltverleih</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>https://www.showsystem.de</t>
+          <t>https://www.zepra-event.de</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Kombiniert Zelte und Eventtechnik – Strombedarf im Freien</t>
+          <t>Full-Service inkl. Technik- und Zeltverleih, Outdoor-Events</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5039,50 +5079,54 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Franze Event &amp; Rental</t>
+          <t>Prolite Event GmbH</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Schwarzer Stamm 1</t>
+          <t>Hauptstraße 11/1</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>06842</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dessau-Roßlau</t>
+          <t>Haigerloch-Owingen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Eventverleih</t>
+          <t>Licht-/Ton-/Bühnentechnik &amp; Event-Service</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>https://www.event-miet.de</t>
+          <t>https://www.prolite.de</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Verleiht Partyzelte, Bühnen und PA – Strom für draußen</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>Mittelständischer Eventtechnikbetrieb Zollernalb</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Impressum-Stand 1-4 Jahre alt – vor Versand prüfen</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5090,47 +5134,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Party San GmbH</t>
+          <t>AlbLive Veranstaltungstechnik UG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Schwanseestraße 20</t>
+          <t>Waibachstraße 8</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>99423</t>
+          <t>72116</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Weimar</t>
+          <t>Mössingen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Thüringen</t>
+          <t>Baden-Württemberg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Festival-Veranstalter</t>
+          <t>Veranstaltungstechnik Verleih</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>https://www.party-san.de</t>
+          <t>https://www.alblive.de</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Metal-Open-Air auf Flugplatzgelände braucht großen mobilen Strombedarf</t>
+          <t>Junger inhabergeführter Verleih, Vereins-/Dorffeste Schwäbische Alb</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5141,50 +5185,54 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Omega Veranstaltungstechnik Jürgen Schneider</t>
+          <t>DAXL Veranstaltungstechnik e.K.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Döbereinerstraße 26</t>
+          <t>Gutenbergstraße 41</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>99427</t>
+          <t>64289</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Weimar</t>
+          <t>Darmstadt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Thüringen</t>
+          <t>Hessen</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ost</t>
+          <t>Süd – lokale VT</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Veranstaltungstechnik</t>
+          <t>Ton-/Licht-/Bühnentechnik Verleih &amp; Service</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>https://omega-weimar.de</t>
+          <t>https://www.daxl-veranstaltungstechnik.de</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Technik für Stadtfeste und Sportevents braucht leisen Strom</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>Etablierter Verleih mit Online-Mietkatalog, Darmstadt</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Lager Mornewegstr. 43B</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5192,50 +5240,3366 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>Hübsch Licht Ton Events (Peter Hübsch)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Gallusweg 3</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>78183</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Hüfingen</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Süd – lokale VT</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Licht-/Ton-Verleih, Eventdeko</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>https://huebsch24.de</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Inhabergeführt, Verleih Licht/Ton und Deko, Schwarzwald-Baar</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Impressum-Stand 1-4 Jahre alt – vor Versand prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SKOPP Zelt+Event (Wolfgang Skopp)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Auf der Beune 50</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>64839</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Münster (bei Dieburg)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Süd – lokale VT</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Zelt- &amp; Eventverleih</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.skopp-zelt-event.de</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Zelt-/Eventverleih für Feste, Strom auf freier Fläche nötig</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Beattec Veranstaltungstechnik (Jonas Baur)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Michael-Kitzelmann-Straße 5</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>88167</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Gestratz</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Süd – lokale VT</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik Verleih</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>https://beattec.de</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Kleiner inhabergeführter Verleih, Westallgäu/Bodensee-Raum</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>LK Lindau (Allgäu), Randgebiet</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VOK DAMS Events GmbH</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Katernberger Straße 54</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>42115</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Wuppertal</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Eventagentur</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vokdams.de</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Live-Marketing-Events weltweit, oft Outdoor-Locations ohne Netzanschluss</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Uniplan GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Schanzenstraße 39 a/b</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>51063</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Eventagentur / Messebau</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.uniplan.com</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Markenerlebnisse und Messestände, temporäre Installationen brauchen Strom</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SOUND BROS. GmbH</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ettore-Bugatti-Str. 43</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>51149</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik (Ton/Licht-Verleih)</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.soundbros.de</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Ton- und Lichtverleih, leiser Strom für Open-Air-Einsätze</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Procon Event GmbH (Procon Veranstaltungstechnik)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Eygelshovener Straße 10</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>50999</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>https://procon-veranstaltungstechnik.de</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Licht-Ton-Bühnentechnik für Events, Ersatz für laute Generatoren</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Verzeichnisse nennen noch Frangenheimstraße</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Parookaville GmbH</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Katharinenquartier 4-6</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>47652</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Weeze</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.parookaville.com</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Großfestival mit Camping, Bühnen, Food-Ständen, hoher mobiler Strombedarf</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Raum3 Konzertveranstaltungs GmbH (Haldern Pop)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Lindenstraße 1b</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>46459</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Rees-Haldern</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>https://haldernpop.com</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Ländliches Open-Air-Festival, emissionsfreie Stromversorgung für Nebenbühnen</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Contour Festival Organisations GmbH (Summerjam)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hemmelrather Weg 241</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>51377</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Leverkusen</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>https://summerjam.de</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Open-Air am Fühlinger See, Stromversorgung für Bühnen und Stände</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>satis&amp;fy AG</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Industriegebiet Dögelmühle</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>61184</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Karben</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik / Bühnenbau / Eventproduktion</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>https://satis-fy.com</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Großer Eventdienstleister mit Nachhaltigkeitsfokus, Dieselersatz für Produktionen</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Keine Hausnummer im Impressum</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Röder Zelt- und Veranstaltungsservice GmbH</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Am Lautenstein 5</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>63654</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Büdingen</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Zeltverleih / Mobile Raumlösungen</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>https://roder.com</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Temporäre Hallen und VIP-Zelte benötigen netzunabhängige Stromversorgung</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FKP Zelt-Event GmbH</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Im Steinböhl 9</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>69518</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Abtsteinach</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Zeltverleih</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>https://fkp-zelte.de</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Fest- und Eventzelte, leiser Strom für Beleuchtung und Catering</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>WORLD CLUB DOME GmbH</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Schwedlerstraße 1-5</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>60314</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.worldclubdome.com</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Großevents mit vielen Bühnen und Backstage-Strombedarf</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>I-Motion GmbH Events &amp; Communication (Nature One)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Am Hohen Stein 8</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>56218</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Mülheim-Kärlich</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nature-one.de</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Festival auf ehemaligem Raketengelände, große Camping- und Floorflächen</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MBE Licht- und Tontechnik (Marcus Bochert)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hauptstraße 12</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>56598</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Rheinbrohl</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbe-licht-ton.de</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Licht- und Tontechnik für Vereins- und Stadtfeste ohne Stromanschluss</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>M. Franzreb &amp; Söhne GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sachsenhütter Straße 8</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>67098</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Bad Dürkheim</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Zeltverleih / Zeltbau</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>https://franzreb-zelte.de</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Festzeltbetrieb für Weinfeste, Strom für Licht und Ausschank</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Zeltverleih Ernst GmbH</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Rat-Tressel-Straße 29b</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>66636</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Tholey</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Saarland</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Zeltverleih</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zeltverleih-ernst.de</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Party- und Festzelte, Strom für private und gewerbliche Feiern</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Saar-Lor-Lux-Zelte GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Konrad-Zuse-Straße 8</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Kirkel</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Saarland</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Zeltverleih / Eventlogistik / Catering</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>https://saar-lor-lux-zelte.eu</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Zelte, Zeltheizungen und Catering-Verbund, hoher mobiler Strombedarf</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Laut &amp; Leise Veranstaltungstechnik (Dirk Langer)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Hochwaldstraße 34</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>66679</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Losheim am See</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Saarland</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik (PA/Licht/Bühne-Verleih)</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.llv-langer.de</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Vermietung PA, Licht und Bühnen, mobile Stromlösung als Zusatzangebot</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Presented for People GmbH &amp; Co. KG (Rocco del Schlacko)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Europaallee 6</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>66113</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Saarbrücken</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Saarland</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Festival- und Konzertveranstalter</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rocco-del-schlacko.de</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Open-Air-Veranstalter, Strombedarf für Bühnen und Gelände</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Festival laut Website beendet – schwacher Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>WOA Festival GmbH (Wacken Open Air)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Schenefelder Str. 17</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>25596</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Wacken</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wacken.com</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Riesiges Festivalgelände mit vielen Bühnen und Camping, hoher Bedarf an Dieselersatz</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FKP Scorpio Konzertproduktionen GmbH</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Große Elbstraße 277a</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>22767</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>https://fkpscorpio.com</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Veranstaltet Hurricane und weitere Open-Airs, hat eine Nachhaltigkeitsstrategie</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LCe Event &amp; Technik GmbH</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ottensener Straße 8</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>22525</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>https://lce-hamburg.de</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Ton-, Licht- und Messetechnik, mobiler Strom für Außeneinsätze</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Karsten Jahnke Konzertdirektion GmbH</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Lerchenstraße 12</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>22767</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Konzert- und Festivalveranstalter</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>https://kj.de</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Open-Air-Konzerte brauchen leise Stromversorgung für Bühne und Backstage</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Kopf &amp; Steine GmbH (MS Dockville)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Eduardstraße 46</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>20257</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>https://msdockville.de</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Festival auf Industriebrache, Nachbarn verlangen leise und emissionsfreie Stromquellen</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Impressum evtl. älter</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ESK Events &amp; Promotion GmbH (Deichbrand)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Otto-Lilienthal-Straße 1</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>27639</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Wurster Nordseeküste</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>https://deichbrand.de</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Großes Festival auf einem Flugplatz ohne festes Stromnetz</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Kulturkosmos Müritz e.V. (Fusion Festival)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Am Flugplatz 1</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>17248</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Lärz</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mecklenburg-Vorpommern</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>https://fusion-festival.de</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Festival mit Öko-Anspruch und vielen dezentralen Bühnen ohne Netzanschluss</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Airbeat One GmbH Zweigniederlassung</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Paulstraße 2a</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>19249</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Lübtheen</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mecklenburg-Vorpommern</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>https://airbeat-one.de</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Großes Elektrofestival mit Campingflächen, Strom für Infrastruktur nötig</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Hannover Concerts GmbH &amp; Co. KG Betriebsgesellschaft</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ferdinand-Wilhelm-Fricke-Weg 8</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>30169</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Konzertveranstalter</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hannover-concerts.de</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Betreibt Open-Air-Bühnen und -Konzerte, Strom für Nebenflächen</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Rent.Group Hamburg/Bremen GmbH (Party.Rent Hamburg)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Senefelder-Ring 80</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>21465</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Reinbek</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Eventmobiliar-Verleih</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.partyrent.com/de/eventverleih-hamburg</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Verleiht Eventausstattung, Powerstations wären eine sinnvolle Ergänzung im Mietsortiment</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Störtebeker Festspiele GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Am Bodden 100</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>18528</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Ralswiek</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mecklenburg-Vorpommern</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Open-Air-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stoertebeker.de</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Naturbühne im Landschaftsschutzgebiet, dort zählen leise und emissionsfreie Stromquellen</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Reload Event GmbH</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Rudolf-Diesel-Straße 5</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>27232</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Sulingen</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>https://reload-festival.de</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Metal-Festival auf freiem Gelände, braucht Strom für Camping und Stände</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Adresse aus Shop-AGB/Datenschutz</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Baltic Eventmanagement GmbH (Baltic Open Air)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Schmiederedder 8</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>24357</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Fleckeby</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>https://www.baltic-open-air.de</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Open-Air auf freier Fläche, braucht mobile Stromversorgung</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HAMKE Event &amp; Messe (Jan-Mirko Hamke)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Dorfstraße 150</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>25336</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Klein Nordende</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Veranstaltungs- und Messetechnik</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>https://hamke.biz</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Event- und Messetechnik, mobile Akkus für Außeneinsätze</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Otter Veranstaltungstechnik GbR</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Haart 224</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>24539</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Neumünster</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik und Bühnenbau</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.otter-veranstaltungstechnik.de</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Vermietet Licht, Ton und Bühnen, Strom als Zusatzmietartikel</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Laut Website keine Abholadresse</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Großmarkt Rostock GmbH</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hanseatenstraße 5</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>18146</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Rostock</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mecklenburg-Vorpommern</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Markt- und Großveranstalter</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.grossmarkt-rostock.de</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Veranstaltet Weihnachts- und Spezialmärkte, Marktstände brauchen mobilen Strom</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>MEISSNER EXPO GmbH</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Industriestraße 11</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Halstenbek</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Messebau</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>https://meissner-expo.de</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Nachhaltiger Messebauer, Strom für Outdoor-Stände und Aufbauphasen</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ZELTCITY GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Jägerstieg 5</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>21465</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Wentorf bei Hamburg</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Zeltverleih</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zeltcity.de</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Zeltveranstaltungen auf Freiflächen brauchen Strom für Licht und Catering</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>PLZ nicht direkt im Impressum bestätigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Bührmann Gruppe GmbH</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Hamfhofsweg 133</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>28357</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Event und Gastronomie</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>https://buehrmann-gruppe.de</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Eventlocation Lankenauer Höft und Catering, Strom für Außen- und Strandevents</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CK Catering Kontor Hamburg GmbH</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ausschläger Weg 36-38</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>20537</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Event-Catering</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>https://cateringkontor.de</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Catering bis 4000 Gäste, mobiler Strom für Außenküchen</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Frontsound Veranstaltungstechnik GmbH</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Stöhrerstraße 3e</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>04347</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.frontsound.de</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Ton-, Licht- und Videotechnik bei Events braucht leisen mobilen Strom</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Messeprojekt GmbH</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Bergweg 7</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>04356</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Messebau</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>https://messeprojekt.de</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Messestände und Events brauchen emissionsfreien Strom in Hallen</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>dd show &amp; eventgroup</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Wirtschaftsweg 2a</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>04420</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Markranstädt</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bühnenbau/Eventvermietung</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eventmodul-vermietung.de</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Mobile Bühnen und Showküchen im Freien brauchen netzunabhängigen Strom</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Nachtdigital GmbH</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Friedensstr. 20</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>04774</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Dahlen</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>https://nachtdigital.de</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Open-Air-Festival im Grünen mit Bedarf an leisen Stromquellen</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HMG Events GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>An der Prießnitzaue 32</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>01328</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Bühnenbau/Eventausstattung</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hmg-rentals.de</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Bühnen- und Infrastrukturverleih für Open Airs ohne Netzanschluss</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PAW pa-world GmbH (Turbo Events)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Behringstr. 34</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>01159</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>https://turbo-events.de</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Fullservice-Eventtechnik braucht Strom an Orten ohne Netzanschluss</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>nuck GmbH</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Nikolaus-Otto-Str. 11</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>02625</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Bautzen</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Zeltverleih</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nuck.de</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Festzelte und Bühnen brauchen Beleuchtungs- und Cateringstrom</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Der Event Service</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Bahnhofstraße 4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>09228</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Chemnitz</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.der-event-service.de</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Ton, Licht und Bühne mit Mietpark für Außenveranstaltungen</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>tec4you GbR</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Schönherrstraße 8</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>09113</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Chemnitz</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Sachsen</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik/Mobilbühnen</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>https://tec4you.eu</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Mobilbühnen bundesweit im Einsatz brauchen leise Stromversorgung</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>blue media event GmbH</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Wichertstraße 47</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>10439</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>https://blue-media.de</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Berliner Eventtechnikverleih – Innenstadtevents ohne Dieselgenerator</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>VEITLIGHT Martin Veit</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Möllendorffstr. 52</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Licht- und Tontechnikverleih</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>https://licht-und-tontechnikverleih.de</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Licht und Ton für Partys im Freien in Berlin-Brandenburg</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Rorbach Event + Sound</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Havelländer Ring 38</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>https://rorbach-events.com</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Konferenz- und Eventtechnik braucht leise Pufferstromlösung</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GATE Eventmanagement &amp; Veranstaltungstechnik GmbH</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Salzufer 13-14a</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>10587</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Eventagentur/Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>https://gate-av.de</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Eventmanagement mit Technik für Locations mit schwachem Netzanschluss</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Kontaktseite nennt auch Reuchlinstr. 10-11, 10553 Berlin</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Zeltverleih Heinz Pautz</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Alt-Lübars 38a</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>13469</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Zeltverleih</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zeltverleih-pautz.de</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Fest- und Partyzelte brauchen Strom für Licht und Catering</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Berliner Partyservice Grunke</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Müllerstr. 185</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>13353</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Catering/Imbisswagenverleih</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>https://eventcatering-grunke.de</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Verleiht Imbiss- und Kühlwagen, die netzunabhängigen Strom brauchen</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DTB Veranstaltungstechnik GmbH</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ricarda-Huch-Straße 2</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>14480</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Potsdam</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dtb.berlin</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Fullservice inklusive Stromversorgung für Events in Brandenburg</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Lager: Am Buchhorst 33, 14478 Potsdam</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ferropolis Stiftung Industriekultur gGmbH</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ferropolisstrasse 1</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>06773</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Gräfenhainichen</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Festivalgelände/Veranstalter</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ferropolis.de</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Großes Festivalgelände mit hohem temporärem Strombedarf</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Expovent</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Leipziger Chaussee 193</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>06112</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Halle (Saale)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Eventausstattung/Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>https://expovent.de</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Verleiht Bühnen, Zelte und Technik, die Strom brauchen</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Impressum ca. 6 Jahre alt – vor Versand prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ESS Emmes Sound Service</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Holleber Weg 14</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>06128</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Halle (Saale)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ess-veranstaltungstechnik.de</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Bühnen-, Licht- und Tontechnik für Events in Halle</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Adresse am schwächsten belegt – vor Versand prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Showsystem Fabian Stankewitz</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Satteldorfer Straße 13</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>39397</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Gröningen</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik/Zeltverleih</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.showsystem.de</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Kombiniert Zelte und Eventtechnik – Strombedarf im Freien</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Franze Event &amp; Rental</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Schwarzer Stamm 1</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>06842</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Dessau-Roßlau</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Eventverleih</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>https://www.event-miet.de</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Verleiht Partyzelte, Bühnen und PA – Strom für draußen</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Party San GmbH</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Schwanseestraße 20</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>99423</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Weimar</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Thüringen</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Festival-Veranstalter</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.party-san.de</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Metal-Open-Air auf Flugplatzgelände braucht großen mobilen Strombedarf</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Omega Veranstaltungstechnik Jürgen Schneider</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Döbereinerstraße 26</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>99427</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Weimar</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Thüringen</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Veranstaltungstechnik</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>https://omega-weimar.de</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Technik für Stadtfeste und Sportevents braucht leisen Strom</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>TAXIS Steffen Köhler</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>Dorfstraße 23</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>07768</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>Reinstädt</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Thüringen</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>Ost</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>Zeltverleih/Eventausstattung</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>https://www.taxis-thueringen.de</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J156" t="inlineStr">
         <is>
           <t>Festzelte und Eventausstattung brauchen Strom ohne Dieselgenerator</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5330,10 +8694,74 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId92"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId156"/>
   </tableParts>
 </worksheet>
 </file>